--- a/students/Navruzov Gamzabeg/Laba3/ЛР3. ОЦЕНКА ПРОЕКТА.xlsx
+++ b/students/Navruzov Gamzabeg/Laba3/ЛР3. ОЦЕНКА ПРОЕКТА.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\warrior\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A1E188C-5D2A-499E-A7B8-43EED65373C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6865CAE-313C-4B17-AE09-3C2CB9286A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -432,13 +432,19 @@
   <si>
     <t>Совещания, планёрки, ретроспективы, отчётность</t>
   </si>
+  <si>
+    <t>Внедрение</t>
+  </si>
+  <si>
+    <t>Менеджмент проекта</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -812,7 +818,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2043,7 +2049,7 @@
         <v>74</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="E47" s="22"/>
       <c r="F47" s="23"/>
@@ -2111,7 +2117,7 @@
         <v>75</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="E51" s="22"/>
       <c r="F51" s="23"/>
